--- a/Compititor's_Price/Recticel_Prices/Recticel_Prices_14-07-2026.xlsx
+++ b/Compititor's_Price/Recticel_Prices/Recticel_Prices_14-07-2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Priyanka\Documents\Price_Comp_Dashboard\Compititor's_Price\Recticel_Prices\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CE795A7-09BD-4585-9390-42C6B5A6881D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E9A1190-0367-4ADF-84BE-AFAB1DD0FC9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6030" yWindow="1710" windowWidth="21600" windowHeight="11070" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2775" yWindow="2355" windowWidth="21600" windowHeight="11070" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="258">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="262">
   <si>
     <t>SKU</t>
   </si>
@@ -794,6 +794,18 @@
   </si>
   <si>
     <t>£716.05</t>
+  </si>
+  <si>
+    <t>£18.31</t>
+  </si>
+  <si>
+    <t>£28.83</t>
+  </si>
+  <si>
+    <t>£39.98</t>
+  </si>
+  <si>
+    <t>£48.84</t>
   </si>
 </sst>
 </file>
@@ -1321,7 +1333,7 @@
         <v>28</v>
       </c>
       <c r="Q3" t="s">
-        <v>28</v>
+        <v>258</v>
       </c>
       <c r="R3" t="s">
         <v>41</v>
@@ -1489,7 +1501,7 @@
         <v>28</v>
       </c>
       <c r="Q6" t="s">
-        <v>28</v>
+        <v>259</v>
       </c>
       <c r="R6" t="s">
         <v>75</v>
@@ -1601,7 +1613,7 @@
         <v>28</v>
       </c>
       <c r="Q8" t="s">
-        <v>28</v>
+        <v>241</v>
       </c>
       <c r="R8" t="s">
         <v>95</v>
@@ -1769,7 +1781,7 @@
         <v>28</v>
       </c>
       <c r="Q11" t="s">
-        <v>28</v>
+        <v>260</v>
       </c>
       <c r="R11" t="s">
         <v>126</v>
@@ -1825,7 +1837,7 @@
         <v>28</v>
       </c>
       <c r="Q12" t="s">
-        <v>28</v>
+        <v>261</v>
       </c>
       <c r="R12" t="s">
         <v>26</v>

--- a/Compititor's_Price/Recticel_Prices/Recticel_Prices_14-07-2026.xlsx
+++ b/Compititor's_Price/Recticel_Prices/Recticel_Prices_14-07-2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Priyanka\Documents\Price_Comp_Dashboard\Compititor's_Price\Recticel_Prices\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E9A1190-0367-4ADF-84BE-AFAB1DD0FC9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0C3088B-5EB5-492F-ADBD-BC99EE7C6D23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2775" yWindow="2355" windowWidth="21600" windowHeight="11070" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="35475" yWindow="2895" windowWidth="21600" windowHeight="11070" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="262">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="263">
   <si>
     <t>SKU</t>
   </si>
@@ -806,6 +806,9 @@
   </si>
   <si>
     <t>£48.84</t>
+  </si>
+  <si>
+    <t>£276.59</t>
   </si>
 </sst>
 </file>
@@ -2075,7 +2078,7 @@
         <v>179</v>
       </c>
       <c r="C17" t="s">
-        <v>28</v>
+        <v>262</v>
       </c>
       <c r="D17" t="s">
         <v>28</v>
